--- a/data.xlsx
+++ b/data.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1087.62</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>DAVALYNDA</t>
+          <t>CLARISSA</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>DAVALYNDA EDELINE</t>
+          <t>CLARISSA THALIA</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -5871,24 +5871,24 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/DAVALYNDA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/CLARISSA.webp</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>24.79</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>DAVALYNDA</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>DAVALYNDA EDELINE</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -5903,24 +5903,24 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/DAVID.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/DAVALYNDA.webp</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>52.17</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>DERRYLIA</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>DERRYLIA MUTIARA FASHA</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -5935,24 +5935,24 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/DERRYLIA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/DAVID.webp</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>430.49</t>
+          <t>29.89</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>DEVA</t>
+          <t>DERRYLIA</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>DEVA CHANDRA</t>
+          <t>DERRYLIA MUTIARA FASHA</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -5967,24 +5967,24 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/DEVA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/DERRYLIA.webp</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>318.19</t>
+          <t>430.49</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>EVELYN</t>
+          <t>DEVA</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>EVELYN NATASHA_</t>
+          <t>DEVA CHANDRA</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -5999,24 +5999,24 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/EVELYN.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/DEVA.webp</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>120.64</t>
+          <t>318.19</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>FABYANDRA</t>
+          <t>EVELYN</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>FABYANDRA PUTRA SETIAWAN</t>
+          <t>EVELYN NATASHA</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -6031,24 +6031,24 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/FABYANDRA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/EVELYN.webp</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>120.64</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>FELICITASKOMALASARIUTAMI</t>
+          <t>FABYANDRA</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>FELICITASKOMALASARIUTAMI</t>
+          <t>FABYANDRA PUTRA SETIAWAN</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -6063,24 +6063,24 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/FELICITASKOMALASARIUTAMI.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/FABYANDRA.webp</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>89.46</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>FREYA</t>
+          <t>FELICITASKOMALASARIUTAMI</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>FREYA TATIANNA LIMANUS</t>
+          <t>FELICITASKOMALASARIUTAMI</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -6095,24 +6095,24 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/FREYA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/FELICITASKOMALASARIUTAMI.webp</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>423.37</t>
+          <t>40.17</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>HAIKAL</t>
+          <t>FREYA</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>HAIKAL AMIRULLAH PUTRA PRIBOWO</t>
+          <t>FREYA TATIANNA LIMANUS</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -6127,24 +6127,24 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/HAIKAL.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/FREYA.webp</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>216.03</t>
+          <t>423.37</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>HARLAN</t>
+          <t>HAIKAL</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>HARLAN JOHANES PARJUANGAN TAMBUNAN</t>
+          <t>HAIKAL AMIRULLAH PUTRA PRIBOWO</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -6159,24 +6159,24 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/HARLAN.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/HAIKAL.webp</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>216.03</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>JENNA</t>
+          <t>HARLAN</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>JENNA ADRIANA KARAMOY</t>
+          <t>HARLAN JOHANES PARJUANGAN TAMBUNAN</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -6191,24 +6191,24 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/JENNA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/HARLAN.webp</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>54.17</t>
+          <t>31.06</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>JESAQUEEN</t>
+          <t>JENNA</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>JESAQUEEN RACHEL</t>
+          <t>JENNA ADRIANA KARAMOY</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -6223,24 +6223,24 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/JESAQUEEN.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JENNA.webp</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>239.68</t>
+          <t>54.17</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>JESSICANATALIE</t>
+          <t>JESAQUEEN</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>JESSICA NATALIE GERALDINE</t>
+          <t>JESAQUEEN RACHEL</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -6255,24 +6255,24 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/JESSICANATALIE.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JESAQUEEN.webp</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>148.30</t>
+          <t>239.68</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>JOANNA</t>
+          <t>JESSICANATALIE</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>JOANNA CLARENCE ISABEL</t>
+          <t>JESSICA NATALIE GERALDINE</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -6287,24 +6287,24 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/JOANNA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JESSICANATALIE.webp</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>73.73</t>
+          <t>148.30</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>JONATHANCHANDRA</t>
+          <t>JOANNA</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>JONATHAN CHANDRA</t>
+          <t>JOANNA CLARENCE ISABEL</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -6319,24 +6319,24 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/JONATHANCHANDRA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JOANNA.webp</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>86.71</t>
+          <t>73.73</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>JONATHANEDBERT</t>
+          <t>JONATHANCHANDRA</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>JONATHAN EDBERT SANTOSO</t>
+          <t>JONATHAN CHANDRA</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -6351,24 +6351,24 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/JONATHANEDBERT.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JONATHANCHANDRA.webp</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>120.16</t>
+          <t>86.71</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>JOSEPHINE</t>
+          <t>JONATHANEDBERT</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>JOSEPHINE ANNABELLA WITARSA</t>
+          <t>JONATHAN EDBERT SANTOSO</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -6383,24 +6383,24 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/JOSEPHINE.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JONATHANEDBERT.webp</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>120.16</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>KATHERINA</t>
+          <t>JOSEPHINE</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>KATHERINA LEA SETIYONO</t>
+          <t>JOSEPHINE ANNABELLA WITARSA</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -6415,24 +6415,24 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/KATHERINA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JOSEPHINE.webp</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>299.37</t>
+          <t>35.08</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>KAYLA</t>
+          <t>JOSHUA</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>KAYLA TINAYA</t>
+          <t>JOSHUA IVANDER HARTAWAN</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -6447,24 +6447,24 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/KAYLA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JOSHUA.webp</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>267.79</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>KELVIN</t>
+          <t>JUSTINEESTEVAN</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>KELVIN FULVIANO PRANATA</t>
+          <t>JUSTINEESTEVAN</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -6479,24 +6479,24 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/KELVIN.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/JUSTINEESTEVAN.webp</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>154.42</t>
+          <t>10.91</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>LADY</t>
+          <t>KATHERINA</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>LADY SERENITY</t>
+          <t>KATHERINA LEA SETIYONO</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -6511,24 +6511,24 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/LADY.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/KATHERINA.webp</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>284.05</t>
+          <t>299.37</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>LOUISE</t>
+          <t>KAYLA</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>LOUISE LIORA</t>
+          <t>KAYLA TINAYA</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -6543,24 +6543,24 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/LOUISE.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/KAYLA.webp</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>283.49</t>
+          <t>41.41</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>MARCELO</t>
+          <t>KELVIN</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>MARCELO EVAN HERMAWAN</t>
+          <t>KELVIN FULVIANO PRANATA</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -6575,24 +6575,24 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/MARCELO.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/KELVIN.webp</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>294.52</t>
+          <t>154.42</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>MARSYA</t>
+          <t>LADY</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>MARSYA ADRIANI M</t>
+          <t>LADY SERENITY</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -6607,24 +6607,24 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/MARSYA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/LADY.webp</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>284.05</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>MICHELLIN</t>
+          <t>LOUISE</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>MICHELLIN PALIT</t>
+          <t>LOUISE LIORA</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -6639,24 +6639,24 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/MICHELLIN.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/LOUISE.webp</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>47.80</t>
+          <t>283.49</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>MOZA</t>
+          <t>MARCELO</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>MOZA DINATA RAISHA_</t>
+          <t>MARCELO EVAN HERMAWAN</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -6671,24 +6671,24 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/MOZA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/MARCELO.webp</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>83.95</t>
+          <t>294.52</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>MUHAMMADDZAKY</t>
+          <t>MARSYA</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>MUHAMMAD DZAKY PUTRA CAHYADI</t>
+          <t>MARSYA ADRIANI M</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -6703,24 +6703,24 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/MUHAMMADDZAKY.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/MARSYA.webp</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>161.07</t>
+          <t>44.05</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>NAFTALINO</t>
+          <t>MATTHEWFERNANDO</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>NAFTALINO MALOMA TANZIL</t>
+          <t>MATTHEW FERNANDO SHELDON</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -6735,24 +6735,24 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/NAFTALINO.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/MATTHEWFERNANDO.webp</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>114.46</t>
+          <t>487.30</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>MICHELLIN</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>NATALIA SUJADI</t>
+          <t>MICHELLIN PALIT</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -6767,24 +6767,24 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/NATALIA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/MICHELLIN.webp</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>65.01</t>
+          <t>47.80</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>NINGSIH</t>
+          <t>MOZA</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>NINGSIH SRI HASTUTI</t>
+          <t>MOZA DINATA RAISHA</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -6799,24 +6799,24 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/NINGSIH.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/MOZA.webp</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>163.74</t>
+          <t>83.95</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>RAYHAN</t>
+          <t>MUHAMMADDZAKY</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>RAYHAN FERDINAND A.</t>
+          <t>MUHAMMAD DZAKY PUTRA CAHYADI</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/RAYHAN.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/MUHAMMADDZAKY.webp</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>519.13</t>
+          <t>161.07</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>REZON</t>
+          <t>NADINE</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>REZON ALBION</t>
+          <t>NADINE MARCIA KAWITONO</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -6863,24 +6863,24 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/REZON.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/NADINE.webp</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>255.49</t>
+          <t>181.75</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ROW</t>
+          <t>NAFTALINO</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>ROW1_ QUEENNA PRICILLA</t>
+          <t>NAFTALINO MALOMA TANZIL</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -6895,24 +6895,24 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/ROW.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/NAFTALINO.webp</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>1046.67</t>
+          <t>114.46</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ROWMATTHEW</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>ROW1_MATTHEW FERNANDO SHELDON</t>
+          <t>NATALIA SUJADI</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -6927,24 +6927,24 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/ROWMATTHEW.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/NATALIA.webp</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>487.30</t>
+          <t>65.01</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ROWJOSHUA</t>
+          <t>NINGSIH</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>ROW2_JOSHUA IVANDER HARTAWAN</t>
+          <t>NINGSIH SRI HASTUTI</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -6959,24 +6959,24 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/ROWJOSHUA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/NINGSIH.webp</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>267.79</t>
+          <t>163.74</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ROWNADINE</t>
+          <t>QUEENNA</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>ROW2_NADINE MARCIA KAWITONO</t>
+          <t>QUEENNA PRICILLA</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -6991,24 +6991,24 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/ROWNADINE.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/QUEENNA.webp</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>181.75</t>
+          <t>1046.67</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ROWYOCELYN</t>
+          <t>RAYHAN</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>ROW2_YOCELYN BERNESSA</t>
+          <t>RAYHAN FERDINAND A.</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -7023,24 +7023,24 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/ROWYOCELYN.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/RAYHAN.webp</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>145.71</t>
+          <t>519.13</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ROWJUSTINEESTEVAN</t>
+          <t>REZON</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>ROW3_JUSTINEESTEVAN</t>
+          <t>REZON ALBION</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -7055,24 +7055,24 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/ROWJUSTINEESTEVAN.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/REZON.webp</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>255.49</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ROWCLARISSA</t>
+          <t>TANIA</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>ROW5_CLARISSA THALIA</t>
+          <t>TANIA AMANDA SENTOSA</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -7087,24 +7087,24 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/ROWCLARISSA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/TANIA.webp</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>40.83</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>TANIA</t>
+          <t>THERY</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>TANIA AMANDA SENTOSA</t>
+          <t>THERY YOUCHELIN</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -7119,24 +7119,24 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/TANIA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/THERY.webp</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>58.53</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>THERY</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>THERY YOUCHELIN</t>
+          <t>VALENCIA MARLYN</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -7151,24 +7151,24 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/THERY.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/VALENCIA.webp</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>337.90</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>WARILY</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>VALENCIA MARLYN</t>
+          <t>WARILY TISSA KARTANA</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -7183,24 +7183,24 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/VALENCIA.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/WARILY.webp</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>337.90</t>
+          <t>192.19</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>WARILY</t>
+          <t>YOCELYN</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>WARILY TISSA KARTANA</t>
+          <t>YOCELYN BERNESSA</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>assets/photos/07. PIC - ARTHA/WARILY.webp</t>
+          <t>assets/photos/07. PIC - ARTHA/YOCELYN.webp</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>192.19</t>
+          <t>145.71</t>
         </is>
       </c>
     </row>
